--- a/program/tab4.xlsx
+++ b/program/tab4.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,17 +10,17 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4AB15D-6AFE-4A20-8C87-5AD080F4B7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="3">
   <si>
     <t>w1</t>
   </si>
@@ -34,8 +34,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -56,7 +56,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -66,43 +66,45 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -121,7 +123,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
@@ -272,7 +274,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -296,9 +298,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -322,7 +324,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -357,7 +359,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -375,7 +377,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -400,7 +402,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -436,16 +438,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="5.140625" style="2" customWidth="true"/>
+    <col min="3" max="3" width="6.140625" style="2" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -456,70 +458,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2.5</v>
       </c>
       <c r="B2" s="6">
-        <v>5388.2030413573748</v>
+        <v>5387.8255712524624</v>
       </c>
       <c r="C2" s="6">
-        <v>4256.5486910064528</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4256.2741158957506</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3</v>
       </c>
       <c r="B3" s="6">
-        <v>5631.7817570710286</v>
+        <v>5631.4248817331463</v>
       </c>
       <c r="C3" s="6">
-        <v>4433.2901812019918</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4433.0318670989509</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3.5</v>
       </c>
       <c r="B4" s="6">
-        <v>5826.6172612290384</v>
+        <v>5826.2792370020116</v>
       </c>
       <c r="C4" s="6">
-        <v>4574.0428882459664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4573.799162342365</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>5986.6473211863286</v>
+        <v>5986.3263632713642</v>
       </c>
       <c r="C5" s="6">
-        <v>4689.2490763184269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4689.0183756898932</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>4.5</v>
       </c>
       <c r="B6" s="6">
-        <v>6120.8366396767624</v>
+        <v>6120.5310938208959</v>
       </c>
       <c r="C6" s="6">
-        <v>4785.5780924674164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4785.3590345842722</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>5</v>
       </c>
       <c r="B7" s="6">
-        <v>6235.2450551839092</v>
+        <v>6234.9534436868244</v>
       </c>
       <c r="C7" s="6">
-        <v>4867.5127196069861</v>
+        <v>4867.3041047740981</v>
       </c>
     </row>
   </sheetData>

--- a/program/tab4.xlsx
+++ b/program/tab4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="39" uniqueCount="3">
   <si>
     <t>w1</t>
   </si>
@@ -463,10 +463,10 @@
         <v>2.5</v>
       </c>
       <c r="B2" s="6">
-        <v>5387.8255712524624</v>
+        <v>5293.8941239150363</v>
       </c>
       <c r="C2" s="6">
-        <v>4256.2741158957506</v>
+        <v>4187.8810025445182</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
@@ -474,10 +474,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="6">
-        <v>5631.4248817331463</v>
+        <v>5528.7032245559285</v>
       </c>
       <c r="C3" s="6">
-        <v>4433.0318670989509</v>
+        <v>4358.6026157465358</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
@@ -485,10 +485,10 @@
         <v>3.5</v>
       </c>
       <c r="B4" s="6">
-        <v>5826.2792370020116</v>
+        <v>5716.2434788271039</v>
       </c>
       <c r="C4" s="6">
-        <v>4573.799162342365</v>
+        <v>4494.3736583259843</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
@@ -496,10 +496,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>5986.3263632713642</v>
+        <v>5870.0951029409316</v>
       </c>
       <c r="C5" s="6">
-        <v>4689.0183756898932</v>
+        <v>4605.3782985260186</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
@@ -507,10 +507,10 @@
         <v>4.5</v>
       </c>
       <c r="B6" s="6">
-        <v>6120.5310938208959</v>
+        <v>5998.97411189778</v>
       </c>
       <c r="C6" s="6">
-        <v>4785.3590345842722</v>
+        <v>4698.1083412766147</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
@@ -518,10 +518,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="6">
-        <v>6234.9534436868244</v>
+        <v>6108.7617401779044</v>
       </c>
       <c r="C7" s="6">
-        <v>4867.3041047740981</v>
+        <v>4776.9201489746738</v>
       </c>
     </row>
   </sheetData>

--- a/program/tab4.xlsx
+++ b/program/tab4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="39" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="3">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab4.xlsx
+++ b/program/tab4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="45" uniqueCount="3">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab4.xlsx
+++ b/program/tab4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="45" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="3">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab4.xlsx
+++ b/program/tab4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="3">
   <si>
     <t>w1</t>
   </si>
